--- a/artfynd/A 48352-2022 artfynd.xlsx
+++ b/artfynd/A 48352-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,54 +680,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69507145</v>
+        <v>137446694</v>
       </c>
       <c r="B2" t="n">
-        <v>87309</v>
+        <v>87647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3674</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+          <t>Norrhagen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685099</v>
+        <v>685117</v>
       </c>
       <c r="R2" t="n">
-        <v>6687391</v>
+        <v>6687380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,17 +741,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 ex. under gran.</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,80 +762,66 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik barrskog.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69507145</t>
+          <t>https://artportalen.se/Sighting/137446694</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69529594</v>
+        <v>137443779</v>
       </c>
       <c r="B3" t="n">
-        <v>93209</v>
+        <v>87482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+          <t>Norrhagen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685076</v>
+        <v>685020</v>
       </c>
       <c r="R3" t="n">
-        <v>6687323</v>
+        <v>6687317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,17 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>7 ex. under gran.</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,80 +864,66 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik barrskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69529594</t>
+          <t>https://artportalen.se/Sighting/137443779</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75891282</v>
+        <v>137444531</v>
       </c>
       <c r="B4" t="n">
-        <v>89143</v>
+        <v>87482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4405</v>
+        <v>445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+          <t>Norrhagen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685115</v>
+        <v>685055</v>
       </c>
       <c r="R4" t="n">
-        <v>6687378</v>
+        <v>6687344</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,17 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 ex. i mossvegetation under gran och hassel.</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,80 +966,66 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik barrskog med inslag av hassel.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75891282</t>
+          <t>https://artportalen.se/Sighting/137444531</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69563217</v>
+        <v>137442601</v>
       </c>
       <c r="B5" t="n">
-        <v>91443</v>
+        <v>96643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5754</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+          <t>Norrhagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685040</v>
+        <v>685032</v>
       </c>
       <c r="R5" t="n">
-        <v>6687335</v>
+        <v>6687365</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,17 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex.</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,27 +1068,4290 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik barrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137442601</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137445591</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96643</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>685127</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6687386</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445591</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>69507145</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>685099</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6687391</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2003-10-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2003-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69507145</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137445137</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87553</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>685114</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6687389</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445137</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137445105</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87390</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>685123</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6687393</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445105</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>69529594</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>685076</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6687323</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2003-10-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2003-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>7 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69529594</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137442552</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93494</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>685036</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6687360</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442552</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137443173</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93494</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>685067</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6687341</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137443173</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137443296</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93494</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>685062</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6687346</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137443296</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>75891282</v>
+      </c>
+      <c r="B14" t="n">
+        <v>89143</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>685115</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6687378</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2003-10-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2003-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 ex. i mossvegetation under gran och hassel.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog med inslag av hassel.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75891282</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137442402</v>
+      </c>
+      <c r="B15" t="n">
+        <v>89391</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>685032</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6687368</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442402</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137444943</v>
+      </c>
+      <c r="B16" t="n">
+        <v>89391</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>685102</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6687388</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444943</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137445713</v>
+      </c>
+      <c r="B17" t="n">
+        <v>89391</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>685162</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6687385</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445713</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137443637</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93153</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>685027</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6687319</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137443637</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137444597</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93153</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>685071</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6687379</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444597</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>69563217</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Strömmen 3 km NNV om Östhammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>685040</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6687335</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/69563217</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137442316</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>685044</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6687367</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442316</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137442590</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>685029</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6687362</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442590</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137443338</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>685067</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6687345</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137443338</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137444030</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>685007</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6687268</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444030</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137444051</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>684989</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6687260</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444051</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137444079</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>684980</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6687279</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444079</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137444672</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>685074</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6687376</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444672</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137444854</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>685090</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6687360</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444854</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137445639</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>685124</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6687379</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445639</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137445647</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>685132</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6687391</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445647</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137445684</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>685137</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6687393</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445684</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137445729</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>685175</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6687397</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445729</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137445881</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>685121</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6687363</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445881</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137445891</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>685117</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6687359</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445891</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137445939</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93518</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>685107</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6687345</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445939</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137443943</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4789</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>685026</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6687299</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående döende gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137443943</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137442937</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99409</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>685044</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6687354</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442937</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137444743</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99409</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>685075</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6687380</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444743</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137445022</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99409</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>685110</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6687391</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445022</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137445812</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99409</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>685167</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6687386</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445812</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137446192</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99409</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>685103</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6687330</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137446192</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137446794</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99409</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>685083</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6687423</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137446794</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137442648</v>
+      </c>
+      <c r="B43" t="n">
+        <v>111427</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>685033</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6687377</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442648</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137443688</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101647</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>685027</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6687321</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137443688</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137444952</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101647</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>685107</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6687386</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444952</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137446830</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101647</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>685087</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6687429</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137446830</t>
         </is>
       </c>
     </row>
@@ -1168,6 +5361,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48352-2022 artfynd.xlsx
+++ b/artfynd/A 48352-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137446694</v>
       </c>
       <c r="B2" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>137443779</v>
       </c>
       <c r="B3" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>137444531</v>
       </c>
       <c r="B4" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>137442601</v>
       </c>
       <c r="B5" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>137445591</v>
       </c>
       <c r="B6" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>137445137</v>
       </c>
       <c r="B8" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>137445105</v>
       </c>
       <c r="B9" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137442552</v>
       </c>
       <c r="B11" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137443173</v>
       </c>
       <c r="B12" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>137443296</v>
       </c>
       <c r="B13" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137442402</v>
       </c>
       <c r="B15" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>137444943</v>
       </c>
       <c r="B16" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137445713</v>
       </c>
       <c r="B17" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137443637</v>
       </c>
       <c r="B18" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137444597</v>
       </c>
       <c r="B19" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>137442316</v>
       </c>
       <c r="B21" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>137442590</v>
       </c>
       <c r="B22" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>137443338</v>
       </c>
       <c r="B23" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137444030</v>
       </c>
       <c r="B24" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>137444051</v>
       </c>
       <c r="B25" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>137444079</v>
       </c>
       <c r="B26" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>137444672</v>
       </c>
       <c r="B27" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>137444854</v>
       </c>
       <c r="B28" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>137445639</v>
       </c>
       <c r="B29" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>137445647</v>
       </c>
       <c r="B30" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137445684</v>
       </c>
       <c r="B31" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137445729</v>
       </c>
       <c r="B32" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>137445881</v>
       </c>
       <c r="B33" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>137445891</v>
       </c>
       <c r="B34" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>137445939</v>
       </c>
       <c r="B35" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137443943</v>
+        <v>137468358</v>
       </c>
       <c r="B36" t="n">
-        <v>4789</v>
+        <v>93521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102306</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685026</v>
+        <v>685128</v>
       </c>
       <c r="R36" t="n">
-        <v>6687299</v>
+        <v>6687385</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4290,17 +4290,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående döende gran</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4326,16 +4321,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137443943</t>
+          <t>https://artportalen.se/Sighting/137468358</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137442937</v>
+        <v>137443943</v>
       </c>
       <c r="B37" t="n">
-        <v>99409</v>
+        <v>4789</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4343,21 +4338,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4367,10 +4362,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685044</v>
+        <v>685026</v>
       </c>
       <c r="R37" t="n">
-        <v>6687354</v>
+        <v>6687299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4405,6 +4400,11 @@
           <t>2026-10-25</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående döende gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4428,16 +4428,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137442937</t>
+          <t>https://artportalen.se/Sighting/137443943</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137444743</v>
+        <v>137442937</v>
       </c>
       <c r="B38" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685075</v>
+        <v>685044</v>
       </c>
       <c r="R38" t="n">
-        <v>6687380</v>
+        <v>6687354</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4530,16 +4530,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137444743</t>
+          <t>https://artportalen.se/Sighting/137442937</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137445022</v>
+        <v>137444743</v>
       </c>
       <c r="B39" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685110</v>
+        <v>685075</v>
       </c>
       <c r="R39" t="n">
-        <v>6687391</v>
+        <v>6687380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4632,16 +4632,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137445022</t>
+          <t>https://artportalen.se/Sighting/137444743</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137445812</v>
+        <v>137445022</v>
       </c>
       <c r="B40" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685167</v>
+        <v>685110</v>
       </c>
       <c r="R40" t="n">
-        <v>6687386</v>
+        <v>6687391</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4734,16 +4734,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137445812</t>
+          <t>https://artportalen.se/Sighting/137445022</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137446192</v>
+        <v>137445812</v>
       </c>
       <c r="B41" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685103</v>
+        <v>685167</v>
       </c>
       <c r="R41" t="n">
-        <v>6687330</v>
+        <v>6687386</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4836,16 +4836,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137446192</t>
+          <t>https://artportalen.se/Sighting/137445812</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137446794</v>
+        <v>137446192</v>
       </c>
       <c r="B42" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685083</v>
+        <v>685103</v>
       </c>
       <c r="R42" t="n">
-        <v>6687423</v>
+        <v>6687330</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4938,16 +4938,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137446794</t>
+          <t>https://artportalen.se/Sighting/137446192</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137442648</v>
+        <v>137446794</v>
       </c>
       <c r="B43" t="n">
-        <v>111427</v>
+        <v>99412</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4955,21 +4955,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220240</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685033</v>
+        <v>685083</v>
       </c>
       <c r="R43" t="n">
-        <v>6687377</v>
+        <v>6687423</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5040,16 +5040,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137442648</t>
+          <t>https://artportalen.se/Sighting/137446794</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137443688</v>
+        <v>137442648</v>
       </c>
       <c r="B44" t="n">
-        <v>101647</v>
+        <v>111430</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5057,21 +5057,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685027</v>
+        <v>685033</v>
       </c>
       <c r="R44" t="n">
-        <v>6687321</v>
+        <v>6687377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5142,16 +5142,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137443688</t>
+          <t>https://artportalen.se/Sighting/137442648</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137444952</v>
+        <v>137443688</v>
       </c>
       <c r="B45" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685107</v>
+        <v>685027</v>
       </c>
       <c r="R45" t="n">
-        <v>6687386</v>
+        <v>6687321</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,11 +5221,6 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5249,16 +5244,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137444952</t>
+          <t>https://artportalen.se/Sighting/137443688</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137446830</v>
+        <v>137444952</v>
       </c>
       <c r="B46" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5290,10 +5285,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685087</v>
+        <v>685107</v>
       </c>
       <c r="R46" t="n">
-        <v>6687429</v>
+        <v>6687386</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5328,6 +5323,11 @@
           <t>2026-10-25</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5350,6 +5350,108 @@
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444952</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137446830</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>685087</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6687429</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137446830</t>
         </is>
@@ -5402,6 +5504,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48352-2022 artfynd.xlsx
+++ b/artfynd/A 48352-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5148,32 +5148,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137443688</v>
+        <v>137497756</v>
       </c>
       <c r="B45" t="n">
-        <v>101650</v>
+        <v>102566</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685027</v>
+        <v>684997</v>
       </c>
       <c r="R45" t="n">
-        <v>6687321</v>
+        <v>6687319</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,12 +5213,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,13 +5244,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137443688</t>
+          <t>https://artportalen.se/Sighting/137497756</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137444952</v>
+        <v>137443688</v>
       </c>
       <c r="B46" t="n">
         <v>101650</v>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685107</v>
+        <v>685027</v>
       </c>
       <c r="R46" t="n">
-        <v>6687386</v>
+        <v>6687321</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5323,11 +5323,6 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5351,13 +5346,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137444952</t>
+          <t>https://artportalen.se/Sighting/137443688</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137446830</v>
+        <v>137444952</v>
       </c>
       <c r="B47" t="n">
         <v>101650</v>
@@ -5392,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685087</v>
+        <v>685107</v>
       </c>
       <c r="R47" t="n">
-        <v>6687429</v>
+        <v>6687386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,6 +5425,11 @@
           <t>2026-10-25</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5452,6 +5452,108 @@
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137444952</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137446830</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Norrhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>685087</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6687429</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137446830</t>
         </is>
@@ -5505,6 +5607,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48352-2022 artfynd.xlsx
+++ b/artfynd/A 48352-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137446694</v>
       </c>
       <c r="B2" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>137443779</v>
       </c>
       <c r="B3" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>137444531</v>
       </c>
       <c r="B4" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>137442601</v>
       </c>
       <c r="B5" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>137445591</v>
       </c>
       <c r="B6" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>137445137</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>137445105</v>
       </c>
       <c r="B9" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137442552</v>
       </c>
       <c r="B11" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137443173</v>
       </c>
       <c r="B12" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>137443296</v>
       </c>
       <c r="B13" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137442402</v>
       </c>
       <c r="B15" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>137444943</v>
       </c>
       <c r="B16" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137445713</v>
       </c>
       <c r="B17" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137443637</v>
       </c>
       <c r="B18" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137444597</v>
       </c>
       <c r="B19" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>137442316</v>
       </c>
       <c r="B21" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>137442590</v>
       </c>
       <c r="B22" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>137443338</v>
       </c>
       <c r="B23" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137444030</v>
       </c>
       <c r="B24" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>137444051</v>
       </c>
       <c r="B25" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>137444079</v>
       </c>
       <c r="B26" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>137444672</v>
       </c>
       <c r="B27" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>137444854</v>
       </c>
       <c r="B28" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>137445639</v>
       </c>
       <c r="B29" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>137445647</v>
       </c>
       <c r="B30" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137445684</v>
       </c>
       <c r="B31" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137445729</v>
       </c>
       <c r="B32" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>137445881</v>
       </c>
       <c r="B33" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>137445891</v>
       </c>
       <c r="B34" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>137445939</v>
       </c>
       <c r="B35" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>137468358</v>
       </c>
       <c r="B36" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>137442937</v>
       </c>
       <c r="B38" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>137444743</v>
       </c>
       <c r="B39" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>137445022</v>
       </c>
       <c r="B40" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137445812</v>
       </c>
       <c r="B41" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137446192</v>
       </c>
       <c r="B42" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137446794</v>
       </c>
       <c r="B43" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>137442648</v>
       </c>
       <c r="B44" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137497756</v>
       </c>
       <c r="B45" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>137443688</v>
       </c>
       <c r="B46" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137444952</v>
       </c>
       <c r="B47" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>137446830</v>
       </c>
       <c r="B48" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
